--- a/task100Child.xlsx
+++ b/task100Child.xlsx
@@ -1,18 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="26722"/>
+  <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="570" windowWidth="27495" windowHeight="9405" activeTab="2"/>
+    <workbookView xWindow="520" yWindow="580" windowWidth="27500" windowHeight="9400" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet Index" sheetId="4" r:id="rId2"/>
+    <sheet name="Relationships" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1400,37 +1405,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="38.140625" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="34.85546875" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="38.1640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="7.5" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="34.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
     <col min="11" max="11" width="54" customWidth="1"/>
     <col min="12" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="7.5703125" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="17.28515625" customWidth="1"/>
-    <col min="20" max="20" width="15.42578125" customWidth="1"/>
-    <col min="21" max="21" width="18.5703125" customWidth="1"/>
+    <col min="14" max="14" width="7.5" customWidth="1"/>
+    <col min="15" max="15" width="10.5" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" customWidth="1"/>
+    <col min="20" max="20" width="15.5" customWidth="1"/>
+    <col min="21" max="21" width="18.5" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" customWidth="1"/>
-    <col min="24" max="25" width="16.140625" customWidth="1"/>
-    <col min="26" max="26" width="16.42578125" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" customWidth="1"/>
+    <col min="24" max="25" width="16.1640625" customWidth="1"/>
+    <col min="26" max="26" width="16.5" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" customWidth="1"/>
     <col min="28" max="28" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1516,7 +1521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1547,19 +1552,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" customWidth="1"/>
+    <col min="2" max="2" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -1567,7 +1577,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1577,46 +1587,51 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AC101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="38.140625" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="38.1640625" customWidth="1"/>
+    <col min="2" max="2" width="37.1640625" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" customWidth="1"/>
-    <col min="12" max="12" width="26.42578125" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" customWidth="1"/>
+    <col min="12" max="12" width="26.5" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="7.5703125" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" customWidth="1"/>
-    <col min="17" max="17" width="7.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="10.5" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
-    <col min="19" max="19" width="12.42578125" customWidth="1"/>
-    <col min="20" max="20" width="17.28515625" customWidth="1"/>
-    <col min="21" max="21" width="15.42578125" customWidth="1"/>
-    <col min="22" max="22" width="18.5703125" customWidth="1"/>
-    <col min="23" max="23" width="38.140625" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" customWidth="1"/>
-    <col min="25" max="25" width="37.42578125" customWidth="1"/>
-    <col min="26" max="26" width="16.140625" customWidth="1"/>
-    <col min="27" max="27" width="16.42578125" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="12.5" customWidth="1"/>
+    <col min="20" max="20" width="17.33203125" customWidth="1"/>
+    <col min="21" max="21" width="15.5" customWidth="1"/>
+    <col min="22" max="22" width="18.5" customWidth="1"/>
+    <col min="23" max="23" width="38.1640625" customWidth="1"/>
+    <col min="24" max="24" width="14.6640625" customWidth="1"/>
+    <col min="25" max="25" width="37.5" customWidth="1"/>
+    <col min="26" max="26" width="16.1640625" customWidth="1"/>
+    <col min="27" max="27" width="16.5" customWidth="1"/>
+    <col min="28" max="28" width="11.6640625" customWidth="1"/>
     <col min="29" max="29" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -1705,7 +1720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1740,7 +1755,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1769,7 +1784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1798,7 +1813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1827,7 +1842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1856,7 +1871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1885,7 +1900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1914,7 +1929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1943,7 +1958,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1972,7 +1987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2001,7 +2016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2030,7 +2045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2059,7 +2074,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2088,7 +2103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2117,7 +2132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2146,7 +2161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2175,7 +2190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2204,7 +2219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -2233,7 +2248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2262,7 +2277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2291,7 +2306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2320,7 +2335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2349,7 +2364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2378,7 +2393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2407,7 +2422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2436,7 +2451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2465,7 +2480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2494,7 +2509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2523,7 +2538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2552,7 +2567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2581,7 +2596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -2610,7 +2625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2639,7 +2654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -2668,7 +2683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -2697,7 +2712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -2726,7 +2741,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -2755,7 +2770,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -2784,7 +2799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -2813,7 +2828,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -2842,7 +2857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -2871,7 +2886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -2900,7 +2915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -2929,7 +2944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -2958,7 +2973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -2987,7 +3002,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -3016,7 +3031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -3045,7 +3060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -3074,7 +3089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -3103,7 +3118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23">
       <c r="A50" t="s">
         <v>28</v>
       </c>
@@ -3132,7 +3147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23">
       <c r="A51" t="s">
         <v>28</v>
       </c>
@@ -3161,7 +3176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -3190,7 +3205,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23">
       <c r="A53" t="s">
         <v>28</v>
       </c>
@@ -3219,7 +3234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23">
       <c r="A54" t="s">
         <v>28</v>
       </c>
@@ -3248,7 +3263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23">
       <c r="A55" t="s">
         <v>28</v>
       </c>
@@ -3277,7 +3292,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -3306,7 +3321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -3335,7 +3350,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -3364,7 +3379,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23">
       <c r="A59" t="s">
         <v>28</v>
       </c>
@@ -3393,7 +3408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23">
       <c r="A60" t="s">
         <v>28</v>
       </c>
@@ -3422,7 +3437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -3451,7 +3466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -3480,7 +3495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -3509,7 +3524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -3538,7 +3553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -3567,7 +3582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -3596,7 +3611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -3625,7 +3640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23">
       <c r="A68" t="s">
         <v>28</v>
       </c>
@@ -3654,7 +3669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -3683,7 +3698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -3712,7 +3727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -3741,7 +3756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -3770,7 +3785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -3799,7 +3814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -3828,7 +3843,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -3857,7 +3872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -3886,7 +3901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -3915,7 +3930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -3944,7 +3959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -3973,7 +3988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -4002,7 +4017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -4031,7 +4046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -4060,7 +4075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -4089,7 +4104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -4118,7 +4133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -4147,7 +4162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -4176,7 +4191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23">
       <c r="A87" t="s">
         <v>28</v>
       </c>
@@ -4205,7 +4220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23">
       <c r="A88" t="s">
         <v>28</v>
       </c>
@@ -4234,7 +4249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23">
       <c r="A89" t="s">
         <v>28</v>
       </c>
@@ -4263,7 +4278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23">
       <c r="A90" t="s">
         <v>28</v>
       </c>
@@ -4292,7 +4307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -4321,7 +4336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23">
       <c r="A92" t="s">
         <v>28</v>
       </c>
@@ -4350,7 +4365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23">
       <c r="A93" t="s">
         <v>28</v>
       </c>
@@ -4379,7 +4394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23">
       <c r="A94" t="s">
         <v>28</v>
       </c>
@@ -4408,7 +4423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23">
       <c r="A95" t="s">
         <v>28</v>
       </c>
@@ -4437,7 +4452,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23">
       <c r="A96" t="s">
         <v>28</v>
       </c>
@@ -4466,7 +4481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23">
       <c r="A97" t="s">
         <v>28</v>
       </c>
@@ -4495,7 +4510,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23">
       <c r="A98" t="s">
         <v>28</v>
       </c>
@@ -4524,7 +4539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23">
       <c r="A99" t="s">
         <v>28</v>
       </c>
@@ -4553,7 +4568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23">
       <c r="A100" t="s">
         <v>28</v>
       </c>
@@ -4582,7 +4597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23">
       <c r="A101" t="s">
         <v>28</v>
       </c>
@@ -4613,27 +4628,32 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="37.140625" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.1640625" customWidth="1"/>
+    <col min="2" max="2" width="37.5" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="37.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.5" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" customWidth="1"/>
+    <col min="9" max="9" width="37.1640625" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -4665,7 +4685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -4687,5 +4707,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/task100Child.xlsx
+++ b/task100Child.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="350">
   <si>
     <t>XOR.id</t>
   </si>
@@ -1066,6 +1066,12 @@
   </si>
   <si>
     <t>Task 100</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
   </si>
 </sst>
 </file>
@@ -1562,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="7.1640625" customWidth="1"/>
@@ -1571,17 +1577,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>348</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>39</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>40</v>
       </c>
     </row>
